--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,22 +486,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,19 +517,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,96 +565,92 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -664,35 +660,39 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -728,24 +728,24 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -781,24 +781,24 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -839,44 +839,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -892,44 +892,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -937,31 +937,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,12 +967,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -986,7 +982,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1018,22 +1014,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1043,7 +1039,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1051,27 +1047,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1096,113 +1096,113 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1210,31 +1210,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1244,12 +1240,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1259,7 +1255,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1291,32 +1287,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1324,7 +1320,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1344,22 +1344,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1397,22 +1397,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,19 +1422,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1454,7 +1450,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1464,12 +1460,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1479,7 +1475,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1511,40 +1507,44 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1564,22 +1564,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1597,11 +1597,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1621,32 +1617,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1654,7 +1650,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1662,34 +1662,34 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1710,49 +1710,49 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1780,22 +1780,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1833,32 +1833,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1886,22 +1886,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1911,39 +1911,35 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1953,27 +1949,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2000,32 +1996,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2033,52 +2029,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2106,32 +2106,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2159,32 +2159,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2212,32 +2212,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2265,32 +2265,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2310,6 +2310,59 @@
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,15 +501,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -517,19 +521,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,27 +543,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -570,19 +574,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,22 +596,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -618,61 +622,57 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -680,19 +680,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -733,52 +733,56 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -786,19 +790,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -808,22 +812,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -839,19 +843,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -861,22 +865,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -887,49 +891,49 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -945,44 +949,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -990,56 +994,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1047,46 +1047,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1096,7 +1092,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1104,42 +1100,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1149,15 +1149,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1165,44 +1169,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1218,56 +1222,52 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1275,44 +1275,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1320,56 +1320,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1377,7 +1373,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1397,32 +1397,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1430,7 +1430,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1450,22 +1454,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1475,19 +1479,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1507,22 +1507,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1532,19 +1532,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1564,40 +1560,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1617,7 +1617,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1674,7 +1674,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1684,22 +1684,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1715,44 +1715,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1760,52 +1760,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1816,49 +1820,49 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1886,32 +1890,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1939,89 +1943,85 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2029,109 +2029,109 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2139,52 +2139,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2212,32 +2216,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2265,32 +2269,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2318,32 +2322,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2363,6 +2367,112 @@
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,79 +476,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -558,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -566,7 +562,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -574,19 +574,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -627,19 +627,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -649,22 +649,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -680,19 +680,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -728,96 +728,92 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -827,35 +823,39 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -865,22 +865,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -891,24 +891,24 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -944,24 +944,24 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,22 +971,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1002,44 +1002,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1055,44 +1055,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1100,31 +1100,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1134,12 +1130,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1149,7 +1145,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1181,22 +1177,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1206,7 +1202,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1214,27 +1210,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1259,113 +1259,113 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1373,31 +1373,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1407,12 +1403,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1418,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1454,32 +1450,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1487,7 +1483,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1507,22 +1507,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1560,22 +1560,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1585,19 +1585,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1617,7 +1613,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1627,12 +1623,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1642,7 +1638,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1674,40 +1670,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1727,22 +1727,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1760,11 +1760,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1784,32 +1780,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1817,7 +1813,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1825,34 +1825,34 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1873,49 +1873,49 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1943,22 +1943,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1996,32 +1996,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2049,22 +2049,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2074,39 +2074,35 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2116,27 +2112,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2163,32 +2159,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2196,52 +2192,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2269,32 +2269,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2322,32 +2322,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2375,32 +2375,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2428,32 +2428,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2473,6 +2473,59 @@
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,22 +486,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,19 +517,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,17 +539,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -574,49 +574,49 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -627,19 +627,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -649,22 +649,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -675,57 +675,61 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -733,19 +737,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -755,87 +759,83 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -843,19 +843,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -865,22 +865,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -891,24 +891,24 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -944,77 +944,81 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,22 +1028,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1055,44 +1059,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1103,49 +1107,49 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1153,56 +1157,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1210,56 +1210,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1275,34 +1271,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1312,15 +1308,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1328,44 +1328,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1373,52 +1373,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1426,68 +1430,60 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1495,44 +1491,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1543,49 +1539,49 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1593,7 +1589,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1613,7 +1613,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1623,27 +1623,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1670,22 +1670,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1695,19 +1695,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1727,32 +1723,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1780,7 +1776,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1790,27 +1786,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1837,40 +1833,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1878,44 +1878,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1926,49 +1926,49 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1976,52 +1976,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2032,49 +2036,49 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2102,89 +2106,85 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2192,56 +2192,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2269,85 +2265,89 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2355,52 +2355,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2428,32 +2432,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2481,32 +2485,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2526,6 +2530,222 @@
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>184573</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14403</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6587</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,34 +517,34 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -562,56 +562,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -619,7 +615,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -627,34 +627,34 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -675,96 +675,92 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -774,7 +770,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -782,7 +778,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -790,19 +790,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -843,19 +843,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -865,22 +865,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -896,19 +896,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -944,96 +944,92 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1043,35 +1039,39 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1107,24 +1107,24 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1160,24 +1160,24 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1187,22 +1187,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1218,44 +1218,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1271,44 +1271,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1316,31 +1316,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1350,12 +1346,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1365,7 +1361,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1397,22 +1393,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1418,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1430,27 +1426,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1475,113 +1475,113 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1589,31 +1589,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1623,12 +1619,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1638,7 +1634,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1670,32 +1666,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1703,7 +1699,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1723,22 +1723,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1776,22 +1776,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1801,19 +1801,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1833,7 +1829,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1843,12 +1839,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1858,7 +1854,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1890,40 +1886,44 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1943,22 +1943,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1976,11 +1976,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2000,32 +1996,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2033,7 +2029,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2041,34 +2041,34 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2089,49 +2089,49 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2159,22 +2159,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2212,32 +2212,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2265,22 +2265,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2290,39 +2290,35 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2332,27 +2328,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2379,32 +2375,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2412,52 +2408,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2485,32 +2485,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2538,32 +2538,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2591,32 +2591,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2624,46 +2624,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2673,7 +2669,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2681,52 +2677,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2746,6 +2746,59 @@
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,22 +486,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,19 +517,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -570,34 +570,34 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -615,56 +615,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -672,7 +668,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -680,34 +680,34 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -728,96 +728,92 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -827,7 +823,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -835,7 +831,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -843,19 +843,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -896,19 +896,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -949,19 +949,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -997,96 +997,92 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1096,35 +1092,39 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1160,24 +1160,24 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1213,24 +1213,24 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1271,44 +1271,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1324,44 +1324,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1369,31 +1369,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1403,12 +1399,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1418,7 +1414,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1450,22 +1446,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1475,7 +1471,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1483,27 +1479,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1513,12 +1513,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1528,113 +1528,113 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1642,31 +1642,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1676,12 +1672,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1691,7 +1687,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1723,32 +1719,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1756,7 +1752,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1776,22 +1776,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1829,22 +1829,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1854,19 +1854,15 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1886,7 +1882,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1896,12 +1892,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1911,7 +1907,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1943,40 +1939,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1996,22 +1996,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2029,11 +2029,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2053,32 +2049,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2086,7 +2082,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2094,34 +2094,34 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2142,49 +2142,49 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2212,22 +2212,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2265,32 +2265,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2318,22 +2318,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2343,39 +2343,35 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2385,27 +2381,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2432,32 +2428,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2465,52 +2461,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2538,32 +2538,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2591,32 +2591,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2644,32 +2644,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2677,46 +2677,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2726,7 +2722,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2734,52 +2730,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2799,6 +2799,59 @@
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,35 +501,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,22 +539,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -570,19 +570,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -623,34 +623,34 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,56 +668,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -725,7 +721,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -733,34 +733,34 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -781,96 +781,92 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -880,7 +876,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -888,7 +884,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -896,19 +896,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -949,19 +949,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,22 +971,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1002,19 +1002,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1050,96 +1050,92 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1149,35 +1145,39 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1187,22 +1187,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1213,24 +1213,24 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1266,24 +1266,24 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1324,44 +1324,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1377,44 +1377,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1422,31 +1422,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,12 +1452,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1471,7 +1467,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1503,22 +1499,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1528,7 +1524,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1536,27 +1532,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1581,113 +1581,113 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1695,31 +1695,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1729,12 +1725,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1744,7 +1740,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1776,32 +1772,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1809,7 +1805,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1829,22 +1829,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1882,22 +1882,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1907,19 +1907,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1939,7 +1935,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1949,12 +1945,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1964,7 +1960,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1996,40 +1992,44 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2049,22 +2049,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2082,11 +2082,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2106,32 +2102,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2139,7 +2135,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2147,34 +2147,34 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2195,49 +2195,49 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2265,22 +2265,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2318,32 +2318,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2371,22 +2371,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2396,39 +2396,35 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2438,27 +2434,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2485,32 +2481,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2518,52 +2514,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2591,32 +2591,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2644,32 +2644,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2697,32 +2697,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2730,46 +2730,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2779,7 +2775,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2787,52 +2783,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2852,6 +2852,59 @@
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,35 +501,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,35 +554,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,22 +592,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -623,19 +623,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -676,34 +676,34 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,56 +721,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -778,7 +774,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -786,34 +786,34 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -834,96 +834,92 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -933,7 +929,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -941,7 +937,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -949,19 +949,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1002,19 +1002,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1055,19 +1055,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1103,96 +1103,92 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1202,35 +1198,39 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1266,24 +1266,24 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1319,24 +1319,24 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1346,22 +1346,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1377,44 +1377,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1430,44 +1430,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1475,31 +1475,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1509,12 +1505,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1524,7 +1520,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1556,22 +1552,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1581,7 +1577,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1589,27 +1585,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1634,113 +1634,113 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1748,31 +1748,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1782,12 +1778,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1797,7 +1793,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1829,32 +1825,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1862,7 +1858,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1882,22 +1882,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1935,22 +1935,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1960,19 +1960,15 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1992,7 +1988,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2002,12 +1998,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2017,7 +2013,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2049,40 +2045,44 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2102,22 +2102,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2135,11 +2135,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2159,32 +2155,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2192,7 +2188,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2200,34 +2200,34 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2248,49 +2248,49 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2318,22 +2318,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2371,32 +2371,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2424,22 +2424,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2449,39 +2449,35 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2491,27 +2487,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2538,32 +2534,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2571,52 +2567,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2644,32 +2644,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2697,32 +2697,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2750,32 +2750,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2783,46 +2783,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2832,7 +2828,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2840,52 +2836,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2905,6 +2905,59 @@
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,50 +501,50 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -570,34 +570,34 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,35 +607,39 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,22 +649,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -676,19 +680,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -698,75 +702,75 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -774,56 +778,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -834,24 +834,24 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -861,22 +861,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -914,17 +914,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -949,49 +949,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1002,19 +1002,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1050,57 +1050,61 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1108,19 +1112,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1130,87 +1134,83 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1218,19 +1218,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1266,24 +1266,24 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1319,77 +1319,81 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1399,22 +1403,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1430,44 +1434,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1478,49 +1482,49 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1528,56 +1532,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1585,56 +1585,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1650,34 +1646,34 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1687,15 +1683,19 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1703,44 +1703,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1748,52 +1748,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1801,68 +1805,60 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1870,44 +1866,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1918,49 +1914,49 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1968,7 +1964,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1988,7 +1988,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1998,27 +1998,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2045,22 +2045,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2070,19 +2070,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2102,32 +2098,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2155,7 +2151,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2165,27 +2161,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2212,40 +2208,44 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2253,44 +2253,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2301,49 +2301,49 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2351,52 +2351,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2407,49 +2411,49 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2477,89 +2481,85 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2567,56 +2567,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2644,85 +2640,89 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2730,52 +2730,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2803,32 +2807,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2836,56 +2840,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2913,32 +2913,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2958,6 +2958,169 @@
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>14403</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>6587</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,40 +476,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -517,34 +521,34 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +558,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -582,22 +586,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -615,11 +619,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -639,22 +639,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -664,35 +664,39 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,12 +706,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,35 +721,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -755,12 +759,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,35 +774,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -808,22 +812,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -839,19 +843,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -861,12 +865,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -876,7 +880,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -892,34 +896,34 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -929,7 +933,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -937,56 +941,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -994,7 +994,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1002,34 +1006,34 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1039,7 +1043,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1050,96 +1054,92 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1157,7 +1157,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1165,19 +1169,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1187,12 +1191,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1202,12 +1206,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1218,19 +1222,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1240,22 +1244,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1271,19 +1275,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1293,12 +1297,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1308,7 +1312,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1319,96 +1323,92 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1418,35 +1418,39 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,22 +1460,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1482,24 +1486,24 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1509,12 +1513,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1524,7 +1528,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1535,24 +1539,24 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1562,22 +1566,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1593,44 +1597,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1646,44 +1650,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1691,31 +1695,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1772,22 +1772,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1805,27 +1805,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1835,12 +1839,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1850,113 +1854,113 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1964,31 +1968,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2045,32 +2045,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2078,7 +2078,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2098,22 +2102,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2151,22 +2155,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2176,19 +2180,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2208,7 +2208,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2265,40 +2265,44 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2318,22 +2322,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2343,7 +2347,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2351,11 +2355,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2375,32 +2375,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2408,7 +2408,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2416,34 +2420,34 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2453,7 +2457,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2464,49 +2468,49 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2534,22 +2538,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2559,7 +2563,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2587,32 +2591,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2640,22 +2644,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2665,39 +2669,35 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2707,27 +2707,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2754,32 +2754,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2787,52 +2787,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2860,32 +2864,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2913,32 +2917,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2966,32 +2970,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2999,46 +3003,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3056,52 +3056,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3121,6 +3125,59 @@
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,64 +509,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -574,34 +574,34 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -639,22 +639,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -672,11 +672,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -696,22 +692,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -721,35 +717,39 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -774,35 +774,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -827,35 +827,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -865,22 +865,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -896,19 +896,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -949,34 +949,34 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -994,56 +994,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1051,7 +1047,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1059,34 +1059,34 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1107,96 +1107,92 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1206,7 +1202,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1214,7 +1210,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1222,19 +1222,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1275,19 +1275,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1297,22 +1297,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1328,19 +1328,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1376,96 +1376,92 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1475,35 +1471,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1513,22 +1513,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1539,24 +1539,24 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1592,24 +1592,24 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1619,22 +1619,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1650,44 +1650,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1703,44 +1703,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1748,31 +1748,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1782,12 +1778,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1797,7 +1793,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1829,22 +1825,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1854,7 +1850,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1862,27 +1858,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1907,113 +1907,113 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2021,31 +2021,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2055,12 +2051,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2070,7 +2066,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2102,32 +2098,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2135,7 +2131,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2155,22 +2155,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2208,22 +2208,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2233,19 +2233,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2265,7 +2261,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2275,12 +2271,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2290,7 +2286,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2322,40 +2318,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2375,22 +2375,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2408,11 +2408,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2432,32 +2428,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2465,7 +2461,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2473,34 +2473,34 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2521,49 +2521,49 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2591,22 +2591,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2644,32 +2644,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2697,22 +2697,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2722,39 +2722,35 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2764,27 +2760,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2811,32 +2807,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2844,52 +2840,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2917,32 +2917,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2970,32 +2970,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3023,32 +3023,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3056,46 +3056,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3105,7 +3101,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3113,52 +3109,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3178,6 +3178,59 @@
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,34 +517,34 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -562,64 +562,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -627,34 +627,34 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -692,22 +692,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -725,11 +725,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -749,22 +745,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -774,35 +770,39 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -827,35 +827,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -880,35 +880,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -949,19 +949,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1002,34 +1002,34 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1047,56 +1047,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1104,7 +1100,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1112,34 +1112,34 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1160,96 +1160,92 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1259,7 +1255,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1267,7 +1263,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1275,19 +1275,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1328,19 +1328,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1350,22 +1350,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1381,19 +1381,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1429,96 +1429,92 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1528,35 +1524,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1592,24 +1592,24 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1645,24 +1645,24 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1703,44 +1703,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1756,44 +1756,44 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1801,31 +1801,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1835,12 +1831,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1850,7 +1846,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1882,22 +1878,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1907,7 +1903,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1915,27 +1911,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1960,113 +1960,113 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2074,31 +2074,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2108,12 +2104,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2123,7 +2119,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2155,32 +2151,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2188,7 +2184,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2208,22 +2208,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2261,22 +2261,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2286,19 +2286,15 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2318,7 +2314,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2328,12 +2324,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2343,7 +2339,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2375,40 +2371,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2428,22 +2428,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2461,11 +2461,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2485,32 +2481,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2518,7 +2514,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2526,34 +2526,34 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2574,49 +2574,49 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2644,22 +2644,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2697,32 +2697,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2750,22 +2750,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2775,39 +2775,35 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2817,27 +2813,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2864,32 +2860,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2897,52 +2893,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2970,32 +2970,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3023,32 +3023,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3076,32 +3076,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3109,46 +3109,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3158,7 +3154,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3166,52 +3162,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3231,6 +3231,59 @@
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,50 +486,50 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -570,34 +570,34 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -615,64 +615,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -680,34 +680,34 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -745,22 +745,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -778,11 +778,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -802,22 +798,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -827,35 +823,39 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -880,35 +880,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -933,35 +933,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,22 +971,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1002,19 +1002,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1055,34 +1055,34 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1100,56 +1100,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1157,7 +1153,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1165,34 +1165,34 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1213,96 +1213,92 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1312,7 +1308,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1320,7 +1316,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1328,19 +1328,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1381,19 +1381,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1403,22 +1403,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1434,19 +1434,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1482,96 +1482,92 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1581,35 +1577,39 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1619,22 +1619,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1645,24 +1645,24 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1698,24 +1698,24 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1725,22 +1725,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1756,44 +1756,44 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1854,31 +1854,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1888,12 +1884,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1903,7 +1899,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1935,22 +1931,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1960,7 +1956,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1968,27 +1964,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2013,113 +2013,113 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2127,31 +2127,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2161,12 +2157,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2176,7 +2172,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2208,32 +2204,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2241,7 +2237,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2261,22 +2261,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2314,22 +2314,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2339,19 +2339,15 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2371,7 +2367,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2381,12 +2377,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2396,7 +2392,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2428,40 +2424,44 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2481,22 +2481,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2514,11 +2514,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2538,32 +2534,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2571,7 +2567,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2579,34 +2579,34 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2627,49 +2627,49 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2697,22 +2697,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2750,32 +2750,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2803,22 +2803,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2828,39 +2828,35 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2870,27 +2866,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2917,32 +2913,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2950,52 +2946,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3023,32 +3023,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3076,32 +3076,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3129,32 +3129,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3162,46 +3162,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3211,7 +3207,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3219,52 +3215,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3284,6 +3284,59 @@
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,19 +517,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,50 +539,50 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -623,34 +623,34 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,64 +668,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -733,34 +733,34 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -798,22 +798,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -831,11 +831,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -855,22 +851,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -880,35 +876,39 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -933,35 +933,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -986,35 +986,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1055,19 +1055,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1108,34 +1108,34 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1153,56 +1153,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1210,7 +1206,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1218,34 +1218,34 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1266,96 +1266,92 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1365,7 +1361,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1373,7 +1369,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1381,19 +1381,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1434,19 +1434,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1487,19 +1487,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1535,96 +1535,92 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1634,35 +1630,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1698,24 +1698,24 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1751,24 +1751,24 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1778,22 +1778,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1862,44 +1862,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1907,31 +1907,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1941,12 +1937,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1956,7 +1952,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1988,22 +1984,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2013,7 +2009,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2021,27 +2017,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2066,113 +2066,113 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2180,31 +2180,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2214,12 +2210,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2229,7 +2225,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2261,32 +2257,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2294,7 +2290,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2314,22 +2314,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2367,22 +2367,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2392,19 +2392,15 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2424,7 +2420,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2434,12 +2430,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2449,7 +2445,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2481,40 +2477,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2534,22 +2534,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2567,11 +2567,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2591,32 +2587,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2624,7 +2620,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2632,34 +2632,34 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2680,49 +2680,49 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2750,22 +2750,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2803,32 +2803,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2856,22 +2856,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2881,39 +2881,35 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2923,27 +2919,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2970,32 +2966,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3003,52 +2999,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3076,32 +3076,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3129,32 +3129,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3182,32 +3182,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3215,46 +3215,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3264,7 +3260,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3272,52 +3268,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3337,6 +3337,59 @@
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,40 +476,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -517,19 +521,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +543,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +558,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -570,19 +574,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,50 +596,50 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,12 +649,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,7 +664,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -676,34 +680,34 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -713,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,64 +725,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -786,34 +790,34 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -823,7 +827,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -851,22 +855,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -876,7 +880,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -884,11 +888,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -908,22 +908,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -933,35 +933,39 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,12 +975,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -986,35 +990,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,12 +1028,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1039,35 +1043,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1077,22 +1081,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1108,19 +1112,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1130,12 +1134,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1145,7 +1149,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1161,34 +1165,34 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1198,7 +1202,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1206,56 +1210,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1263,7 +1263,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1271,34 +1275,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1308,7 +1312,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1319,96 +1323,92 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1426,7 +1426,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1434,19 +1438,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,12 +1460,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1471,12 +1475,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1487,19 +1491,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1509,22 +1513,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1540,19 +1544,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1562,12 +1566,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1577,7 +1581,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1588,96 +1592,92 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1687,35 +1687,39 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1725,22 +1729,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1751,24 +1755,24 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1778,12 +1782,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1793,7 +1797,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1804,24 +1808,24 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1831,22 +1835,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1862,44 +1866,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1915,44 +1919,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1960,31 +1964,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2041,22 +2041,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2074,27 +2074,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2104,12 +2108,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2119,113 +2123,113 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2233,31 +2237,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2314,32 +2314,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2347,7 +2347,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2367,22 +2371,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2392,7 +2396,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2420,22 +2424,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2445,19 +2449,15 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2477,7 +2477,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2534,40 +2534,44 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2587,22 +2591,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2612,7 +2616,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2620,11 +2624,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2644,32 +2644,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2677,7 +2677,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2685,34 +2689,34 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2722,7 +2726,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2733,49 +2737,49 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2803,22 +2807,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2828,7 +2832,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2856,32 +2860,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2909,22 +2913,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2934,39 +2938,35 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2976,27 +2976,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3023,32 +3023,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3056,52 +3056,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3129,32 +3133,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3182,32 +3186,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3235,32 +3239,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3268,46 +3272,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3325,52 +3325,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3390,6 +3394,59 @@
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,22 +486,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -521,52 +521,56 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -574,52 +578,56 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -627,44 +635,44 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -672,52 +680,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -725,64 +737,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -790,44 +802,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -843,154 +855,150 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -998,42 +1006,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1043,7 +1055,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1059,34 +1071,34 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1096,88 +1108,92 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1187,22 +1203,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1218,56 +1234,52 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1275,44 +1287,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1323,24 +1335,24 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1350,22 +1362,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1381,109 +1393,109 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1491,44 +1503,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1544,19 +1556,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1566,22 +1578,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1592,102 +1604,106 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1695,11 +1711,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1707,19 +1719,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1729,22 +1741,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1755,24 +1767,24 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1782,22 +1794,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1813,19 +1825,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1835,22 +1847,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1866,97 +1878,101 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1972,39 +1988,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2017,11 +2033,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2029,44 +2041,44 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2074,31 +2086,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2108,22 +2116,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2139,97 +2147,97 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2237,27 +2245,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2267,22 +2279,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2302,44 +2314,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2347,61 +2359,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -2412,44 +2420,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2460,24 +2468,24 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2487,27 +2495,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2534,7 +2542,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2544,27 +2552,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2591,32 +2599,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2644,32 +2652,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2677,11 +2685,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2701,40 +2705,44 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2742,97 +2750,101 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2843,49 +2855,49 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2893,52 +2905,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2949,106 +2965,102 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3056,56 +3068,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3133,32 +3141,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3186,85 +3194,89 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3272,52 +3284,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3325,56 +3341,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3402,32 +3414,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3447,6 +3459,222 @@
         </is>
       </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>184573</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>14403</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>6587</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,31 +509,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -558,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -590,7 +586,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,12 +596,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -647,7 +643,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -657,12 +653,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -672,7 +668,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -704,7 +700,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -714,22 +710,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -749,52 +745,56 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -802,19 +802,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -855,19 +855,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -877,50 +877,50 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -961,34 +961,34 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1006,64 +1006,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1071,34 +1071,34 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1136,22 +1136,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1169,11 +1169,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1193,22 +1189,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1218,35 +1214,39 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1271,35 +1271,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1324,35 +1324,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1362,22 +1362,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1393,19 +1393,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1446,34 +1446,34 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1491,56 +1491,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1548,7 +1544,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1556,34 +1556,34 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1604,96 +1604,92 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1703,7 +1699,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1711,7 +1707,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1719,19 +1719,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1772,19 +1772,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1825,19 +1825,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1873,96 +1873,92 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1972,35 +1968,39 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2010,22 +2010,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2036,24 +2036,24 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2089,24 +2089,24 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2147,44 +2147,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2200,44 +2200,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2245,31 +2245,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2279,12 +2275,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2294,7 +2290,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2326,22 +2322,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2351,7 +2347,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2359,27 +2355,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2404,113 +2404,113 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2518,31 +2518,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2552,12 +2548,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2567,7 +2563,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2599,32 +2595,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2632,7 +2628,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2652,22 +2652,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2705,22 +2705,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2730,19 +2730,15 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2762,7 +2758,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2772,12 +2768,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2787,7 +2783,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2819,40 +2815,44 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2872,22 +2872,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2905,11 +2905,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2929,32 +2925,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2962,7 +2958,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2970,34 +2970,34 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3018,49 +3018,49 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3088,22 +3088,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3141,32 +3141,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3194,22 +3194,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3219,39 +3219,35 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3261,27 +3257,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3308,32 +3304,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3341,52 +3337,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3414,32 +3414,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3467,32 +3467,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3520,32 +3520,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3553,46 +3553,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3602,7 +3598,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3610,52 +3606,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3675,6 +3675,59 @@
         </is>
       </c>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,39 +512,39 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -562,31 +562,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -596,12 +592,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -611,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -643,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -653,12 +649,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -668,7 +664,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -700,7 +696,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -710,12 +706,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -725,7 +721,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -757,7 +753,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -767,22 +763,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -802,52 +798,56 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -855,19 +855,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -908,19 +908,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -930,50 +930,50 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1014,34 +1014,34 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1059,64 +1059,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1124,34 +1124,34 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1189,22 +1189,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1222,11 +1222,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1246,22 +1242,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1271,35 +1267,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1324,35 +1324,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1377,35 +1377,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1415,22 +1415,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1446,19 +1446,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1499,34 +1499,34 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1544,56 +1544,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1601,7 +1597,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1609,34 +1609,34 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1657,96 +1657,92 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1756,7 +1752,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1764,7 +1760,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1772,19 +1772,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1825,19 +1825,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1847,22 +1847,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1878,19 +1878,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1926,96 +1926,92 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2025,35 +2021,39 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2089,24 +2089,24 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2142,24 +2142,24 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2169,22 +2169,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2200,44 +2200,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2253,44 +2253,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2298,31 +2298,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2332,12 +2328,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2347,7 +2343,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2379,22 +2375,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2404,7 +2400,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2412,27 +2408,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2457,113 +2457,113 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2571,31 +2571,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2605,12 +2601,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2620,7 +2616,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2652,32 +2648,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2685,7 +2681,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2705,22 +2705,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2758,22 +2758,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2783,19 +2783,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2815,7 +2811,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2825,12 +2821,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2840,7 +2836,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2872,40 +2868,44 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2925,22 +2925,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2958,11 +2958,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2982,32 +2978,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3015,7 +3011,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3023,34 +3023,34 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3071,49 +3071,49 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3141,22 +3141,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3194,32 +3194,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3247,22 +3247,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3272,39 +3272,35 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3314,27 +3310,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3361,32 +3357,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3394,52 +3390,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3467,32 +3467,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3520,32 +3520,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3573,32 +3573,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3606,46 +3606,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3655,7 +3651,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3663,52 +3659,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3728,6 +3728,59 @@
         </is>
       </c>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,24 +512,24 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,39 +565,39 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -615,31 +615,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -649,12 +645,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -664,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -696,7 +692,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -706,12 +702,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -721,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -753,7 +749,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -763,12 +759,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -778,7 +774,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -810,7 +806,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,22 +816,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -855,52 +851,56 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -908,19 +908,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -961,19 +961,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -983,50 +983,50 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1067,34 +1067,34 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1112,64 +1112,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1177,34 +1177,34 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1242,22 +1242,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1275,11 +1275,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1299,22 +1295,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1324,35 +1320,39 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1377,35 +1377,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1430,35 +1430,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1499,19 +1499,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1552,34 +1552,34 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1597,56 +1597,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1654,7 +1650,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1662,34 +1662,34 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1710,96 +1710,92 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1809,7 +1805,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1817,7 +1813,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1825,19 +1825,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1878,19 +1878,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1900,22 +1900,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1979,96 +1979,92 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2078,35 +2074,39 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2142,24 +2142,24 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2195,24 +2195,24 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2253,44 +2253,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2306,44 +2306,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2351,31 +2351,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2385,12 +2381,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2400,7 +2396,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2432,22 +2428,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2457,7 +2453,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2465,27 +2461,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2510,113 +2510,113 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2624,31 +2624,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2658,12 +2654,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2673,7 +2669,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2705,32 +2701,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2738,7 +2734,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2758,22 +2758,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2811,22 +2811,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2836,19 +2836,15 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2868,7 +2864,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2878,12 +2874,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2893,7 +2889,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2925,40 +2921,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2978,22 +2978,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3011,11 +3011,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3035,32 +3031,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3068,7 +3064,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3076,34 +3076,34 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3124,49 +3124,49 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3194,22 +3194,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3247,32 +3247,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3300,22 +3300,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3325,39 +3325,35 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3367,27 +3363,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3414,32 +3410,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3447,52 +3443,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3520,32 +3520,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3573,32 +3573,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3626,32 +3626,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3659,46 +3659,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3708,7 +3704,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3716,52 +3712,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3781,6 +3781,59 @@
         </is>
       </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,50 +486,50 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,24 +565,24 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -618,39 +618,39 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,31 +668,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,12 +698,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,7 +713,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -749,7 +745,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -759,12 +755,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -774,7 +770,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -806,7 +802,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -816,12 +812,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -831,7 +827,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -863,7 +859,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -873,22 +869,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -908,52 +904,56 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -961,19 +961,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1014,19 +1014,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1036,50 +1036,50 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1120,34 +1120,34 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1165,64 +1165,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1230,34 +1230,34 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1328,11 +1328,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1352,22 +1348,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1377,35 +1373,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1430,35 +1430,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1483,35 +1483,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1521,22 +1521,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1552,19 +1552,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1605,34 +1605,34 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1650,56 +1650,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1707,7 +1703,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1715,34 +1715,34 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1763,96 +1763,92 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1862,7 +1858,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1870,7 +1866,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1878,19 +1878,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1931,19 +1931,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1953,22 +1953,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1984,19 +1984,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2032,96 +2032,92 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2131,35 +2127,39 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2169,22 +2169,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2195,24 +2195,24 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2248,24 +2248,24 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2275,22 +2275,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2306,44 +2306,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2359,44 +2359,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2404,31 +2404,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2438,12 +2434,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2453,7 +2449,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2485,22 +2481,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2510,7 +2506,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2518,27 +2514,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2563,113 +2563,113 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2677,31 +2677,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2711,12 +2707,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2726,7 +2722,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2758,32 +2754,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2791,7 +2787,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2811,22 +2811,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2864,22 +2864,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2889,19 +2889,15 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2921,7 +2917,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2931,12 +2927,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2946,7 +2942,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2978,40 +2974,44 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3031,22 +3031,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3064,11 +3064,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3088,32 +3084,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3121,7 +3117,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3129,34 +3129,34 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3177,49 +3177,49 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3247,22 +3247,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3300,32 +3300,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3353,22 +3353,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3378,39 +3378,35 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3420,27 +3416,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3467,32 +3463,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3500,52 +3496,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3573,32 +3573,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3626,32 +3626,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3679,32 +3679,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3712,46 +3712,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3761,7 +3757,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3769,52 +3765,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3834,6 +3834,59 @@
         </is>
       </c>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,12 +501,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -517,19 +517,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,50 +539,50 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -618,24 +618,24 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -671,39 +671,39 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,31 +721,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -755,12 +751,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,7 +766,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -802,7 +798,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -812,12 +808,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -827,7 +823,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -859,7 +855,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -869,12 +865,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -884,7 +880,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -916,7 +912,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -926,22 +922,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -961,52 +957,56 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1014,19 +1014,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1089,50 +1089,50 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1173,34 +1173,34 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1218,64 +1218,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1283,34 +1283,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1348,22 +1348,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1381,11 +1381,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1405,22 +1401,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1430,35 +1426,39 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1483,35 +1483,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1536,35 +1536,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1574,22 +1574,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1605,19 +1605,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1658,34 +1658,34 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1703,56 +1703,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1760,7 +1756,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1768,34 +1768,34 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1816,96 +1816,92 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1915,7 +1911,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1923,7 +1919,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1931,19 +1931,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1984,19 +1984,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2006,22 +2006,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2037,19 +2037,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2085,96 +2085,92 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2184,35 +2180,39 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2248,24 +2248,24 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2301,24 +2301,24 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2359,44 +2359,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2412,44 +2412,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2457,31 +2457,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2491,12 +2487,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2506,7 +2502,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2538,22 +2534,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2563,7 +2559,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2571,27 +2567,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2616,113 +2616,113 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2730,31 +2730,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2764,12 +2760,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2779,7 +2775,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2811,32 +2807,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2844,7 +2840,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2864,22 +2864,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2917,22 +2917,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2942,19 +2942,15 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2974,7 +2970,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2984,12 +2980,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2999,7 +2995,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3031,40 +3027,44 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3084,22 +3084,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3117,11 +3117,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3141,32 +3137,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3174,7 +3170,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3182,34 +3182,34 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3230,49 +3230,49 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3300,22 +3300,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3353,32 +3353,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3406,22 +3406,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3431,39 +3431,35 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3473,27 +3469,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3520,32 +3516,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3553,52 +3549,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3626,32 +3626,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3679,32 +3679,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3732,32 +3732,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3765,46 +3765,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3814,7 +3810,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3822,52 +3818,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3887,6 +3887,59 @@
         </is>
       </c>
       <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,24 +512,24 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -570,19 +570,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,50 +592,50 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -671,24 +671,24 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -724,39 +724,39 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -774,31 +774,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -808,12 +804,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -823,7 +819,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -855,7 +851,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -865,12 +861,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -880,7 +876,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -912,7 +908,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -922,12 +918,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,7 +933,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -969,7 +965,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -979,22 +975,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1014,52 +1010,56 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1067,19 +1067,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1120,19 +1120,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1142,50 +1142,50 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1226,34 +1226,34 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1271,64 +1271,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1336,34 +1336,34 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1401,22 +1401,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1434,11 +1434,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1458,22 +1454,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1483,35 +1479,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1536,35 +1536,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1589,35 +1589,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1658,19 +1658,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1756,56 +1756,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1813,7 +1809,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1821,34 +1821,34 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1869,96 +1869,92 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1968,7 +1964,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1976,7 +1972,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1984,19 +1984,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2037,19 +2037,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2090,19 +2090,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2138,96 +2138,92 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2237,35 +2233,39 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2275,22 +2275,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2301,24 +2301,24 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2354,24 +2354,24 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2381,22 +2381,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2412,44 +2412,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2465,44 +2465,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2510,31 +2510,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2544,12 +2540,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2559,7 +2555,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2591,22 +2587,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2616,7 +2612,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2624,27 +2620,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2669,113 +2669,113 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2783,31 +2783,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2817,12 +2813,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2832,7 +2828,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2864,32 +2860,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2897,7 +2893,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2917,22 +2917,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2970,22 +2970,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2995,19 +2995,15 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3027,7 +3023,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3037,12 +3033,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3052,7 +3048,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3084,40 +3080,44 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3137,22 +3137,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3170,11 +3170,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3194,32 +3190,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3227,7 +3223,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3235,34 +3235,34 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3283,49 +3283,49 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3353,22 +3353,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3406,32 +3406,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3459,22 +3459,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3484,39 +3484,35 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3526,27 +3522,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3573,32 +3569,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3606,52 +3602,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3679,32 +3679,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3732,32 +3732,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3785,32 +3785,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3818,46 +3818,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3867,7 +3863,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3875,52 +3871,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3940,6 +3940,59 @@
         </is>
       </c>
       <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,34 +517,34 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,24 +565,24 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -623,19 +623,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,50 +645,50 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -724,24 +724,24 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -777,39 +777,39 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -827,31 +827,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -861,12 +857,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -908,7 +904,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,12 +914,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -933,7 +929,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -965,7 +961,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -975,12 +971,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -990,7 +986,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1022,7 +1018,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1032,22 +1028,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1067,52 +1063,56 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1120,19 +1120,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1173,19 +1173,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1195,50 +1195,50 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1324,64 +1324,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1389,34 +1389,34 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1454,22 +1454,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1487,11 +1487,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1511,22 +1507,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1536,35 +1532,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1589,35 +1589,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1642,35 +1642,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1711,19 +1711,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1764,34 +1764,34 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1809,56 +1809,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1866,7 +1862,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1874,34 +1874,34 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1922,96 +1922,92 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2021,7 +2017,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2029,7 +2025,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2037,19 +2037,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2090,19 +2090,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2112,22 +2112,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2143,19 +2143,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2191,96 +2191,92 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2290,35 +2286,39 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2354,24 +2354,24 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2407,24 +2407,24 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2434,22 +2434,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2465,44 +2465,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2518,44 +2518,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2563,31 +2563,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2597,12 +2593,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2612,7 +2608,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2644,22 +2640,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2669,7 +2665,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2677,27 +2673,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2722,113 +2722,113 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2836,31 +2836,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2870,12 +2866,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2885,7 +2881,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2917,32 +2913,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2950,7 +2946,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2970,22 +2970,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3023,22 +3023,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3048,19 +3048,15 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3080,7 +3076,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3090,12 +3086,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3105,7 +3101,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3137,40 +3133,44 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3190,22 +3190,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3223,11 +3223,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3247,32 +3243,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3280,7 +3276,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3288,34 +3288,34 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3336,49 +3336,49 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3406,22 +3406,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3459,32 +3459,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3512,22 +3512,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3537,39 +3537,35 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3579,27 +3575,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3626,32 +3622,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3659,52 +3655,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3732,32 +3732,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3785,32 +3785,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3838,32 +3838,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3871,46 +3871,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3920,7 +3916,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3928,52 +3924,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3993,6 +3993,59 @@
         </is>
       </c>
       <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,22 +486,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,44 +517,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -570,34 +570,34 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -618,24 +618,24 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -676,19 +676,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -698,50 +698,50 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -777,24 +777,24 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -830,39 +830,39 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -880,31 +880,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -914,12 +910,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -929,7 +925,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -961,7 +957,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,12 +967,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -986,7 +982,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1018,7 +1014,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1028,12 +1024,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1043,7 +1039,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1075,7 +1071,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1085,22 +1081,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1120,52 +1116,56 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1173,19 +1173,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1226,19 +1226,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,50 +1248,50 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1332,34 +1332,34 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1377,64 +1377,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1442,34 +1442,34 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1507,22 +1507,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1540,11 +1540,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1564,22 +1560,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1589,35 +1585,39 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1642,35 +1642,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1695,35 +1695,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1733,22 +1733,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1764,19 +1764,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1817,34 +1817,34 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1862,56 +1862,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1919,7 +1915,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1927,34 +1927,34 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1975,96 +1975,92 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2074,7 +2070,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2082,7 +2078,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2090,19 +2090,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2143,19 +2143,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2165,22 +2165,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2196,19 +2196,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2244,96 +2244,92 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2343,35 +2339,39 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2381,22 +2381,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2407,24 +2407,24 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2460,24 +2460,24 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2487,22 +2487,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2518,44 +2518,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2571,44 +2571,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2616,31 +2616,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2650,12 +2646,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2665,7 +2661,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2697,22 +2693,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2722,7 +2718,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2730,27 +2726,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2775,113 +2775,113 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2889,31 +2889,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2923,12 +2919,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2938,7 +2934,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2970,32 +2966,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3003,7 +2999,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3023,22 +3023,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3076,22 +3076,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3101,19 +3101,15 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3133,7 +3129,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3143,12 +3139,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3158,7 +3154,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3190,40 +3186,44 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3243,22 +3243,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3276,11 +3276,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3300,32 +3296,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3333,7 +3329,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3341,34 +3341,34 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3389,49 +3389,49 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3459,22 +3459,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3512,32 +3512,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3565,22 +3565,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3590,39 +3590,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3632,27 +3628,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3679,32 +3675,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3712,52 +3708,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3785,32 +3785,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3838,32 +3838,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3891,32 +3891,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3924,46 +3924,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3973,7 +3969,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3981,52 +3977,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4046,6 +4046,59 @@
         </is>
       </c>
       <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,50 +486,50 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,75 +539,75 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -623,19 +623,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,22 +645,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -671,39 +671,39 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -713,35 +713,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -751,22 +751,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -777,24 +777,24 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -804,27 +804,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -835,19 +835,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -888,34 +888,34 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -933,11 +933,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -945,34 +941,34 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -982,7 +978,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -990,31 +986,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,12 +1016,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1039,7 +1031,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1071,7 +1063,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1081,12 +1073,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1128,7 +1120,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1138,22 +1130,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1173,52 +1165,56 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1226,52 +1222,56 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1279,19 +1279,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1301,50 +1301,50 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1354,65 +1354,65 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1430,117 +1430,117 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1548,34 +1548,34 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1593,11 +1593,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1617,22 +1613,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1642,50 +1638,50 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1695,7 +1691,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1703,7 +1699,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1711,19 +1711,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1764,19 +1764,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1786,50 +1786,50 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1839,22 +1839,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1870,34 +1870,34 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1915,56 +1915,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1975,49 +1971,49 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2025,64 +2021,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2090,19 +2086,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2112,65 +2108,65 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2180,15 +2176,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2196,19 +2196,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2218,27 +2218,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2249,19 +2249,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2271,22 +2271,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2297,61 +2297,57 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2359,19 +2355,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2381,22 +2377,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2412,52 +2408,56 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2465,19 +2465,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2487,22 +2487,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2518,19 +2518,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2540,22 +2540,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2566,49 +2566,49 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2624,44 +2624,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2669,56 +2669,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2726,46 +2722,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2775,7 +2767,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2783,42 +2775,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2828,15 +2824,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2844,44 +2844,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2897,56 +2897,52 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2954,44 +2950,44 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2999,56 +2995,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3056,7 +3048,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3076,32 +3072,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3109,7 +3105,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3129,22 +3129,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3154,19 +3154,15 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3186,22 +3182,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3211,19 +3207,15 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3243,40 +3235,44 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3296,7 +3292,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3306,27 +3302,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3353,7 +3349,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3363,22 +3359,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3394,44 +3390,44 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3439,52 +3435,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3495,49 +3495,49 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3565,32 +3565,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3618,89 +3618,85 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3708,109 +3704,109 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3818,52 +3814,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3891,32 +3891,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3944,32 +3944,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3977,56 +3977,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4054,51 +4050,161 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>14403</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>6587</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>949</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>78439</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
         <is>
           <t>보도자료</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,40 +476,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -517,19 +521,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +543,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +558,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -570,19 +574,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,50 +596,50 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,22 +649,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -676,44 +680,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -729,34 +733,34 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -766,7 +770,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -777,24 +781,24 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -804,12 +808,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -819,12 +823,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -835,19 +839,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,50 +861,50 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -910,12 +914,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -925,7 +929,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -936,24 +940,24 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -963,12 +967,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -978,7 +982,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -989,39 +993,39 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1031,7 +1035,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1039,31 +1043,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1234,7 +1234,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1244,22 +1244,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1279,52 +1279,56 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1332,19 +1336,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1354,12 +1358,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1369,7 +1373,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1385,19 +1389,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1407,50 +1411,50 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1460,12 +1464,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1475,7 +1479,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1491,34 +1495,34 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1528,7 +1532,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1536,64 +1540,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1601,34 +1605,34 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1638,7 +1642,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1666,22 +1670,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1691,7 +1695,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1699,11 +1703,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1723,22 +1723,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1748,35 +1748,39 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1786,12 +1790,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1801,35 +1805,35 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1839,12 +1843,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1854,35 +1858,35 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1892,22 +1896,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1923,19 +1927,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1945,12 +1949,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1960,7 +1964,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1976,34 +1980,34 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2013,7 +2017,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2021,56 +2025,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2078,7 +2078,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2086,34 +2090,34 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2134,96 +2138,92 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2241,7 +2241,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2249,19 +2253,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2271,12 +2275,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2286,12 +2290,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2302,19 +2306,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2324,22 +2328,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2355,19 +2359,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2377,12 +2381,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2392,7 +2396,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2403,96 +2407,92 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2502,35 +2502,39 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2540,22 +2544,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2566,24 +2570,24 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2593,12 +2597,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2608,7 +2612,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2619,24 +2623,24 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2646,22 +2650,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2677,44 +2681,44 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2730,44 +2734,44 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2775,31 +2779,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2856,22 +2856,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2889,27 +2889,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2919,12 +2923,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2934,113 +2938,113 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3048,31 +3052,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3129,32 +3129,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3162,7 +3162,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3182,22 +3186,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3207,7 +3211,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3235,22 +3239,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3260,19 +3264,15 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3292,7 +3292,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3349,40 +3349,44 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3402,22 +3406,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3427,7 +3431,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3435,11 +3439,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3459,32 +3459,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3492,7 +3492,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3500,34 +3504,34 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3537,7 +3541,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3548,49 +3552,49 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3618,22 +3622,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3643,7 +3647,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3671,32 +3675,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3724,22 +3728,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3749,39 +3753,35 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3791,27 +3791,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3838,32 +3838,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3871,52 +3871,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3944,32 +3948,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3997,32 +4001,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4050,32 +4054,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4083,46 +4087,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4140,52 +4140,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4205,6 +4209,59 @@
         </is>
       </c>
       <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,44 +476,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -521,19 +517,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,27 +539,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -574,52 +570,56 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -627,19 +627,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -649,50 +649,50 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,75 +702,75 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -786,19 +786,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -834,39 +834,39 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -876,35 +876,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -914,22 +914,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -940,24 +940,24 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -998,19 +998,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1051,34 +1051,34 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1096,11 +1096,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1108,34 +1104,34 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1145,7 +1141,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1153,31 +1149,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1187,12 +1179,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1202,7 +1194,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1234,7 +1226,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1244,12 +1236,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1291,7 +1283,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1301,22 +1293,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1336,52 +1328,56 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1389,52 +1385,56 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1442,19 +1442,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1464,50 +1464,50 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1517,65 +1517,65 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1593,117 +1593,117 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1711,34 +1711,34 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1756,11 +1756,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1780,22 +1776,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1805,50 +1801,50 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1858,7 +1854,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1866,7 +1862,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1874,19 +1874,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1927,19 +1927,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1949,50 +1949,50 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2002,22 +2002,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2033,34 +2033,34 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2078,56 +2078,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2138,49 +2134,49 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2188,64 +2184,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2253,19 +2249,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2275,65 +2271,65 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2343,15 +2339,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2359,19 +2359,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2381,27 +2381,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -2412,19 +2412,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2434,22 +2434,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2460,61 +2460,57 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2522,19 +2518,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2544,22 +2540,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2575,52 +2571,56 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2628,19 +2628,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2650,22 +2650,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2681,19 +2681,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2703,22 +2703,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2729,49 +2729,49 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2787,44 +2787,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2832,56 +2832,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2889,46 +2885,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2938,7 +2930,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2946,42 +2938,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2991,15 +2987,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3007,44 +3007,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3060,56 +3060,52 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3117,44 +3113,44 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3162,56 +3158,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3219,7 +3211,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3239,32 +3235,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3272,7 +3268,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3292,22 +3292,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3317,19 +3317,15 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3349,22 +3345,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3374,19 +3370,15 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3406,40 +3398,44 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3459,7 +3455,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3469,27 +3465,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3516,7 +3512,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3526,22 +3522,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3557,44 +3553,44 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3602,52 +3598,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3658,49 +3658,49 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3728,32 +3728,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3781,89 +3781,85 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3871,109 +3867,109 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3981,52 +3977,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4054,32 +4054,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4107,32 +4107,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4140,56 +4140,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4217,51 +4213,161 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>14403</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>6587</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>949</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>78439</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
         <is>
           <t>보도자료</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,35 +501,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -570,44 +570,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -615,11 +615,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -627,52 +623,56 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -680,19 +680,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -733,19 +733,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -755,50 +755,50 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -839,44 +839,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -892,34 +892,34 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -940,24 +940,24 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -967,12 +967,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -998,19 +998,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1020,50 +1020,50 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1099,24 +1099,24 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1152,39 +1152,39 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1202,31 +1202,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,12 +1232,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1251,7 +1247,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1283,7 +1279,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1293,12 +1289,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1308,7 +1304,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1340,7 +1336,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1350,12 +1346,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1365,7 +1361,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1397,7 +1393,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1407,22 +1403,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1442,52 +1438,56 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1495,19 +1495,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1548,19 +1548,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1570,50 +1570,50 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1654,34 +1654,34 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1699,64 +1699,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+    